--- a/paper/Tables/Table5_December2018Followup.xlsx
+++ b/paper/Tables/Table5_December2018Followup.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E721D575-B2E1-4BEE-85E8-74CCF6DD6247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-8190" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-8190" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Table5_December2018Followup" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Difference</t>
   </si>
@@ -47,6 +47,48 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Calculator</t>
+  </si>
+  <si>
+    <t>Expired / Dropped</t>
+  </si>
+  <si>
+    <t>Continues</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>Court ruling with payment</t>
+  </si>
+  <si>
+    <t>Court ruling without payment</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Calculator</t>
+  </si>
+  <si>
+    <t>Expired / Dropped</t>
+  </si>
+  <si>
+    <t>Continues</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>Court ruling with payment</t>
+  </si>
+  <si>
+    <t>Court ruling without payment</t>
   </si>
   <si>
     <t>Control</t>
@@ -110,7 +152,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom/>
@@ -120,23 +162,23 @@
       <left/>
       <right/>
       <top style="medium">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -145,45 +187,45 @@
       <right/>
       <top/>
       <bottom style="double">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom style="double">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="true" applyFont="true"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,17 +510,17 @@
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="11" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="11.08984375" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="1" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="12"/>
@@ -494,9 +536,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="2" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>88</v>
@@ -510,9 +552,9 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>77</v>
@@ -538,9 +580,9 @@
         <v>6.4867436492262955</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>267</v>
@@ -566,9 +608,9 @@
         <v>-0.43521880237214344</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -581,9 +623,9 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>174</v>
@@ -598,7 +640,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="7" x14ac:dyDescent="0.35">
       <c r="C7">
         <f>SUM(C2:C6)</f>
         <v>646</v>
@@ -625,7 +667,7 @@
         <v>-7.3435267671061979</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" x14ac:dyDescent="0.35">
       <c r="E8" s="5"/>
       <c r="F8" s="11" t="str">
         <f>B2</f>
@@ -644,20 +686,20 @@
         <v>0.11958455864386486</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" x14ac:dyDescent="0.35">
       <c r="D9" s="3"/>
       <c r="F9" s="11"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" x14ac:dyDescent="0.35">
       <c r="F10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="11" x14ac:dyDescent="0.35">
       <c r="E11" s="2"/>
       <c r="F11" s="11" t="str">
         <f>B3</f>
@@ -676,14 +718,14 @@
         <v>1.1724173616081814</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" x14ac:dyDescent="0.35">
       <c r="D12" s="4"/>
       <c r="F12" s="11"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="F13" s="15" t="s">
         <v>4</v>
       </c>
@@ -700,7 +742,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="15" thickTop="true" x14ac:dyDescent="0.35">
       <c r="I14" s="9"/>
     </row>
   </sheetData>
